--- a/src/test/Receipt_Clear.xlsx
+++ b/src/test/Receipt_Clear.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\API\src\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\git\API\src\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="499"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7760" tabRatio="499"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>Execute</t>
   </si>
@@ -76,33 +76,9 @@
     <t/>
   </si>
   <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>UserEmail</t>
-  </si>
-  <si>
-    <t>S@gmail.com</t>
-  </si>
-  <si>
-    <t>zcac</t>
-  </si>
-  <si>
-    <t>dsfsad@gmail.com</t>
-  </si>
-  <si>
-    <t>sujit</t>
-  </si>
-  <si>
     <t>TestDescription</t>
   </si>
   <si>
-    <t>Verify the Text box</t>
-  </si>
-  <si>
-    <t>Verify the Check box</t>
-  </si>
-  <si>
     <t>0 Min and 0 sec</t>
   </si>
   <si>
@@ -112,41 +88,41 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>com.fasterxml.jackson.databind.exc.InvalidDefinitionException: No serializer found for class Pages.DemoAPI and no properties discovered to create BeanSerializer (to avoid exception, disable SerializationFeature.FAIL_ON_EMPTY_BEANS)</t>
-  </si>
-  <si>
-    <t>SKIP</t>
-  </si>
-  <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
-    <t>java.lang.IllegalArgumentException: body cannot be null</t>
-  </si>
-  <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>0 Min and 1 sec</t>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Get</t>
+  </si>
+  <si>
+    <t>Post</t>
+  </si>
+  <si>
+    <t>0 Min and 3 sec</t>
+  </si>
+  <si>
+    <t>29/12/2024</t>
+  </si>
+  <si>
+    <t>Verify the Get</t>
+  </si>
+  <si>
+    <t>Verify the Post</t>
   </si>
   <si>
     <t>0 Min and 2 sec</t>
-  </si>
-  <si>
-    <t>11/09/2024</t>
-  </si>
-  <si>
-    <t>0 Min and 5 sec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -169,14 +145,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color indexed="1"/>
@@ -194,50 +162,8 @@
       <color indexed="1"/>
       <b val="true"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color indexed="1"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color indexed="1"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color indexed="1"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color indexed="1"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color indexed="1"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color indexed="1"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <color indexed="1"/>
-      <b val="true"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,17 +188,12 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="2"/>
+      <patternFill patternType="solid">
+        <fgColor indexed="58"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="none">
-        <fgColor indexed="58"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="58"/>
       </patternFill>
     </fill>
@@ -312,51 +233,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -703,21 +600,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="8.0" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="9.0" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="16.7109375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="7.7109375" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="19.54296875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="16.7265625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.7265625" collapsed="true"/>
     <col min="6" max="6" bestFit="true" customWidth="true" width="22.0" collapsed="true"/>
-    <col min="7" max="8" bestFit="true" customWidth="true" width="15.28515625" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="18.0"/>
+    <col min="7" max="8" bestFit="true" customWidth="true" width="15.26953125" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="7.54296875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -725,7 +621,7 @@
         <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -743,82 +639,80 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s" s="14">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s" s="6">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1"/>
-    <hyperlink ref="J3" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>